--- a/batch_search_test_input.xlsx
+++ b/batch_search_test_input.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>02 Jun 2026</t>
+          <t>06 Jun 2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>02 Jun 2026</t>
+          <t>06 Jun 2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">

--- a/batch_search_test_input.xlsx
+++ b/batch_search_test_input.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AUMEL</t>
+          <t>CNSGH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Melbourne</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -584,12 +584,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>INMAA</t>
+          <t>INNSA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Nhava Sheva (Mumbai)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -643,6 +643,11 @@
       </c>
       <c r="S2" t="n">
         <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Far East India baseline</t>
+        </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -653,12 +658,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INMAA</t>
+          <t>CNSGH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -668,79 +673,579 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>DEHAM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>12 Jun 2026</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40HC</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>24500</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Freight,Origin Charges</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Factory</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Far East Europe origin nearby</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CNSGH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>USLAX</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>18 Jun 2026</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>20GP</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Freight,Destination Charges</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Dock</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Trans Pacific destination SD</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NLRTM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>USNYC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CY</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>06 Jun 2026</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>24 Jun 2026</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40GP</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>18500</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Freight,Origin Custom Charges,Destination Custom Charges</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Factory</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Europe North America custom</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AEJEA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jebel Ali (Dubai)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>INNSA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nhava Sheva (Mumbai)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>30 Jun 2026</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>20GP</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>51000</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Freight,Origin Charges,Destination Charges</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Factory</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Middle East India SD nearby</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BRSSZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NLRTM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>07 Jul 2026</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40HC</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
-        <v>17000</v>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N7" t="n">
+        <v>9000</v>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>KG</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Freight</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Dock</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>South America Europe freight</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INNSA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nhava Sheva (Mumbai)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SGSIN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>14 Jul 2026</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>20GP</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>14500</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Freight,Origin Charges,Destination Charges</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Factory</t>
         </is>
       </c>
-      <c r="R3" t="n">
+      <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>India SE Asia baseline</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>INR</t>
         </is>
       </c>
     </row>

--- a/batch_search_test_input.xlsx
+++ b/batch_search_test_input.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="70">
   <si>
     <t>Origin Port Code</t>
   </si>
@@ -139,7 +139,91 @@
     <t>Far East Europe origin nearby</t>
   </si>
   <si>
-    <t/>
+    <t>USLAX</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>18 Jun 2026</t>
+  </si>
+  <si>
+    <t>Freight,Destination Charges</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Trans Pacific destination SD</t>
+  </si>
+  <si>
+    <t>NLRTM</t>
+  </si>
+  <si>
+    <t>Rotterdam</t>
+  </si>
+  <si>
+    <t>USNYC</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>24 Jun 2026</t>
+  </si>
+  <si>
+    <t>40GP</t>
+  </si>
+  <si>
+    <t>Freight,Origin Custom Charges,Destination Custom Charges</t>
+  </si>
+  <si>
+    <t>Europe North America custom</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>AEJEA</t>
+  </si>
+  <si>
+    <t>Jebel Ali (Dubai)</t>
+  </si>
+  <si>
+    <t>30 Jun 2026</t>
+  </si>
+  <si>
+    <t>Middle East India SD nearby</t>
+  </si>
+  <si>
+    <t>BRSSZ</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>07 Jul 2026</t>
+  </si>
+  <si>
+    <t>Freight</t>
+  </si>
+  <si>
+    <t>South America Europe freight</t>
+  </si>
+  <si>
+    <t>SGSIN</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>14 Jul 2026</t>
+  </si>
+  <si>
+    <t>India SE Asia baseline</t>
+  </si>
+  <si>
+    <t>INR</t>
   </si>
 </sst>
 </file>
@@ -215,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -228,9 +312,6 @@
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -543,27 +624,27 @@
   <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="21.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="6" width="20.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="26.005" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="6" width="28.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="6" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="6" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="7" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="16.005" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="6" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="6" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="6" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="7" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="7" width="23.005" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="6" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="6" width="19.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="21.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="5" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="26.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="5" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="5" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="5" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="6" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="6" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="5" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="5" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="5" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="6" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="6" width="23.005" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="5" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="5" width="19.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -762,288 +843,328 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>41</v>
+      <c r="G4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="4">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>12000</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R4" s="4">
+        <v>1</v>
+      </c>
+      <c r="S4" s="4">
+        <v>2</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
-      <c r="A5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>41</v>
+      <c r="A5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="4">
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <v>18500</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R5" s="4">
+        <v>1</v>
+      </c>
+      <c r="S5" s="4">
+        <v>1</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
-      <c r="A6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>41</v>
+      <c r="A6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="4">
+        <v>3</v>
+      </c>
+      <c r="N6" s="4">
+        <v>51000</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R6" s="4">
+        <v>3</v>
+      </c>
+      <c r="S6" s="4">
+        <v>5</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
-      <c r="A7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U7" s="5" t="s">
-        <v>41</v>
+      <c r="A7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="4">
+        <v>1</v>
+      </c>
+      <c r="N7" s="4">
+        <v>9000</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R7" s="4">
+        <v>1</v>
+      </c>
+      <c r="S7" s="4">
+        <v>1</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
-      <c r="A8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4"/>
-      <c r="O8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>41</v>
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="4">
+        <v>1</v>
+      </c>
+      <c r="N8" s="4">
+        <v>14500</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R8" s="4">
+        <v>1</v>
+      </c>
+      <c r="S8" s="4">
+        <v>2</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
